--- a/modules/log/Abylai.xlsx
+++ b/modules/log/Abylai.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2863,9 +2863,1813 @@
         <v>57</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B57" t="str">
+        <v>35002</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Сансызбаев Б</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Энгельса (Карасу)(AZ)</v>
+      </c>
+      <c r="E57" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F57" t="str">
+        <v>54105</v>
+      </c>
+      <c r="G57" t="str">
+        <v>47</v>
+      </c>
+      <c r="H57" t="str">
+        <v>168</v>
+      </c>
+      <c r="I57" t="str">
+        <v>121</v>
+      </c>
+      <c r="J57" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K57" t="str">
+        <v>6</v>
+      </c>
+      <c r="L57" t="str">
+        <v>23</v>
+      </c>
+      <c r="M57" t="str">
+        <v>13</v>
+      </c>
+      <c r="N57" t="str">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B58" t="str">
+        <v>32517</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Тогусов</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Ынтымак(AZ)</v>
+      </c>
+      <c r="E58" t="str">
+        <v>6</v>
+      </c>
+      <c r="F58" t="str">
+        <v>51259</v>
+      </c>
+      <c r="G58" t="str">
+        <v>1410</v>
+      </c>
+      <c r="H58" t="str">
+        <v>1439</v>
+      </c>
+      <c r="I58" t="str">
+        <v>29</v>
+      </c>
+      <c r="J58" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K58" t="str">
+        <v>6</v>
+      </c>
+      <c r="L58" t="str">
+        <v>26</v>
+      </c>
+      <c r="M58" t="str">
+        <v>19</v>
+      </c>
+      <c r="N58" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B59" t="str">
+        <v>39637</v>
+      </c>
+      <c r="C59" t="str">
+        <v>КХ "Жас-Нур"</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Фезули(Жанатурмыс)</v>
+      </c>
+      <c r="E59" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F59" t="str">
+        <v>68967</v>
+      </c>
+      <c r="G59" t="str">
+        <v>469</v>
+      </c>
+      <c r="H59" t="str">
+        <v>481</v>
+      </c>
+      <c r="I59" t="str">
+        <v>12</v>
+      </c>
+      <c r="J59" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K59" t="str">
+        <v>7</v>
+      </c>
+      <c r="L59" t="str">
+        <v>1</v>
+      </c>
+      <c r="M59" t="str">
+        <v>15</v>
+      </c>
+      <c r="N59" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B60" t="str">
+        <v>41308</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Таскулова Фатима</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E60" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F60" t="str">
+        <v>79152</v>
+      </c>
+      <c r="G60" t="str">
+        <v>45</v>
+      </c>
+      <c r="H60" t="str">
+        <v>73</v>
+      </c>
+      <c r="I60" t="str">
+        <v>28</v>
+      </c>
+      <c r="J60" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K60" t="str">
+        <v>7</v>
+      </c>
+      <c r="L60" t="str">
+        <v>3</v>
+      </c>
+      <c r="M60" t="str">
+        <v>20</v>
+      </c>
+      <c r="N60" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B61" t="str">
+        <v>40180</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Исмайлов Тофик</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E61" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F61" t="str">
+        <v>72175</v>
+      </c>
+      <c r="G61" t="str">
+        <v>65</v>
+      </c>
+      <c r="H61" t="str">
+        <v>84</v>
+      </c>
+      <c r="I61" t="str">
+        <v>19</v>
+      </c>
+      <c r="J61" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K61" t="str">
+        <v>7</v>
+      </c>
+      <c r="L61" t="str">
+        <v>18</v>
+      </c>
+      <c r="M61" t="str">
+        <v>16</v>
+      </c>
+      <c r="N61" t="str">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B62" t="str">
+        <v>41693</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Каратаев Мукан</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E62" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F62" t="str">
+        <v>80794</v>
+      </c>
+      <c r="G62" t="str">
+        <v>50</v>
+      </c>
+      <c r="H62" t="str">
+        <v>67</v>
+      </c>
+      <c r="I62" t="str">
+        <v>17</v>
+      </c>
+      <c r="J62" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K62" t="str">
+        <v>7</v>
+      </c>
+      <c r="L62" t="str">
+        <v>24</v>
+      </c>
+      <c r="M62" t="str">
+        <v>13</v>
+      </c>
+      <c r="N62" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B63" t="str">
+        <v>35694</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Султанова Гулжан</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E63" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F63" t="str">
+        <v>82456</v>
+      </c>
+      <c r="G63" t="str">
+        <v>21</v>
+      </c>
+      <c r="H63" t="str">
+        <v>36</v>
+      </c>
+      <c r="I63" t="str">
+        <v>15</v>
+      </c>
+      <c r="J63" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K63" t="str">
+        <v>7</v>
+      </c>
+      <c r="L63" t="str">
+        <v>24</v>
+      </c>
+      <c r="M63" t="str">
+        <v>13</v>
+      </c>
+      <c r="N63" t="str">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B64" t="str">
+        <v>40103</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Мырзакулова Венера</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E64" t="str">
+        <v>641</v>
+      </c>
+      <c r="F64" t="str">
+        <v>71541</v>
+      </c>
+      <c r="G64" t="str">
+        <v>260</v>
+      </c>
+      <c r="H64" t="str">
+        <v>276</v>
+      </c>
+      <c r="I64" t="str">
+        <v>16</v>
+      </c>
+      <c r="J64" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K64" t="str">
+        <v>7</v>
+      </c>
+      <c r="L64" t="str">
+        <v>24</v>
+      </c>
+      <c r="M64" t="str">
+        <v>16</v>
+      </c>
+      <c r="N64" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B65" t="str">
+        <v>35002</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Сансызбаев Б</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Энгельса (Карасу)(AZ)</v>
+      </c>
+      <c r="E65" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F65" t="str">
+        <v>83099</v>
+      </c>
+      <c r="G65" t="str">
+        <v>1</v>
+      </c>
+      <c r="H65" t="str">
+        <v>22</v>
+      </c>
+      <c r="I65" t="str">
+        <v>21</v>
+      </c>
+      <c r="J65" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K65" t="str">
+        <v>7</v>
+      </c>
+      <c r="L65" t="str">
+        <v>25</v>
+      </c>
+      <c r="M65" t="str">
+        <v>9</v>
+      </c>
+      <c r="N65" t="str">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B66" t="str">
+        <v>40008</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Кадирбаева Рахима</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Хан Танири (Карасу)</v>
+      </c>
+      <c r="E66" t="str">
+        <v>165</v>
+      </c>
+      <c r="F66" t="str">
+        <v>71220</v>
+      </c>
+      <c r="G66" t="str">
+        <v>166</v>
+      </c>
+      <c r="H66" t="str">
+        <v>175</v>
+      </c>
+      <c r="I66" t="str">
+        <v>9</v>
+      </c>
+      <c r="J66" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K66" t="str">
+        <v>7</v>
+      </c>
+      <c r="L66" t="str">
+        <v>28</v>
+      </c>
+      <c r="M66" t="str">
+        <v>11</v>
+      </c>
+      <c r="N66" t="str">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B67" t="str">
+        <v>40079</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Нышамбаев Бауыржан</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E67" t="str">
+        <v>162</v>
+      </c>
+      <c r="F67" t="str">
+        <v>82942</v>
+      </c>
+      <c r="G67" t="str">
+        <v>1</v>
+      </c>
+      <c r="H67" t="str">
+        <v>180</v>
+      </c>
+      <c r="I67" t="str">
+        <v>179</v>
+      </c>
+      <c r="J67" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K67" t="str">
+        <v>7</v>
+      </c>
+      <c r="L67" t="str">
+        <v>28</v>
+      </c>
+      <c r="M67" t="str">
+        <v>12</v>
+      </c>
+      <c r="N67" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B68" t="str">
+        <v>39982</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Акбаев Жумабек</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Хан Танири (Карасу)</v>
+      </c>
+      <c r="E68" t="str">
+        <v>167</v>
+      </c>
+      <c r="F68" t="str">
+        <v>83138</v>
+      </c>
+      <c r="G68" t="str">
+        <v>1</v>
+      </c>
+      <c r="H68" t="str">
+        <v>55</v>
+      </c>
+      <c r="I68" t="str">
+        <v>54</v>
+      </c>
+      <c r="J68" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K68" t="str">
+        <v>7</v>
+      </c>
+      <c r="L68" t="str">
+        <v>28</v>
+      </c>
+      <c r="M68" t="str">
+        <v>12</v>
+      </c>
+      <c r="N68" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B69" t="str">
+        <v>42066</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Садыкова К</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Нурлы жер (Карасу)</v>
+      </c>
+      <c r="E69" t="str">
+        <v>89</v>
+      </c>
+      <c r="F69" t="str">
+        <v>82573</v>
+      </c>
+      <c r="G69" t="str">
+        <v>16</v>
+      </c>
+      <c r="H69" t="str">
+        <v>36</v>
+      </c>
+      <c r="I69" t="str">
+        <v>20</v>
+      </c>
+      <c r="J69" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K69" t="str">
+        <v>7</v>
+      </c>
+      <c r="L69" t="str">
+        <v>28</v>
+      </c>
+      <c r="M69" t="str">
+        <v>13</v>
+      </c>
+      <c r="N69" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B70" t="str">
+        <v>39977</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Серикбаева Айжан</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E70" t="str">
+        <v>113</v>
+      </c>
+      <c r="F70" t="str">
+        <v>82800</v>
+      </c>
+      <c r="G70" t="str">
+        <v>10</v>
+      </c>
+      <c r="H70" t="str">
+        <v>16</v>
+      </c>
+      <c r="I70" t="str">
+        <v>6</v>
+      </c>
+      <c r="J70" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K70" t="str">
+        <v>7</v>
+      </c>
+      <c r="L70" t="str">
+        <v>28</v>
+      </c>
+      <c r="M70" t="str">
+        <v>13</v>
+      </c>
+      <c r="N70" t="str">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B71" t="str">
+        <v>41316</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Тулебаев Умирзах</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F71" t="str">
+        <v>79160</v>
+      </c>
+      <c r="G71" t="str">
+        <v>320</v>
+      </c>
+      <c r="H71" t="str">
+        <v>336</v>
+      </c>
+      <c r="I71" t="str">
+        <v>16</v>
+      </c>
+      <c r="J71" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K71" t="str">
+        <v>7</v>
+      </c>
+      <c r="L71" t="str">
+        <v>29</v>
+      </c>
+      <c r="M71" t="str">
+        <v>19</v>
+      </c>
+      <c r="N71" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B72" t="str">
+        <v>38305</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Тлемисова А.</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Астана (Карасу)</v>
+      </c>
+      <c r="E72" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F72" t="str">
+        <v>62665</v>
+      </c>
+      <c r="G72" t="str">
+        <v>1</v>
+      </c>
+      <c r="H72" t="str">
+        <v>39</v>
+      </c>
+      <c r="I72" t="str">
+        <v>38</v>
+      </c>
+      <c r="J72" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K72" t="str">
+        <v>7</v>
+      </c>
+      <c r="L72" t="str">
+        <v>30</v>
+      </c>
+      <c r="M72" t="str">
+        <v>22</v>
+      </c>
+      <c r="N72" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B73" t="str">
+        <v>39815</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Белтаева Жайсан</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E73" t="str">
+        <v>1122</v>
+      </c>
+      <c r="F73" t="str">
+        <v>70051</v>
+      </c>
+      <c r="G73" t="str">
+        <v>315</v>
+      </c>
+      <c r="H73" t="str">
+        <v>356</v>
+      </c>
+      <c r="I73" t="str">
+        <v>41</v>
+      </c>
+      <c r="J73" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K73" t="str">
+        <v>8</v>
+      </c>
+      <c r="L73" t="str">
+        <v>8</v>
+      </c>
+      <c r="M73" t="str">
+        <v>10</v>
+      </c>
+      <c r="N73" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B74" t="str">
+        <v>31346</v>
+      </c>
+      <c r="C74" t="str">
+        <v>ЧП "Усманов"</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Жубанов(AZ)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F74" t="str">
+        <v>42702</v>
+      </c>
+      <c r="G74" t="str">
+        <v>23751</v>
+      </c>
+      <c r="H74" t="str">
+        <v>23830</v>
+      </c>
+      <c r="I74" t="str">
+        <v>79</v>
+      </c>
+      <c r="J74" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K74" t="str">
+        <v>8</v>
+      </c>
+      <c r="L74" t="str">
+        <v>19</v>
+      </c>
+      <c r="M74" t="str">
+        <v>13</v>
+      </c>
+      <c r="N74" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B75" t="str">
+        <v>31873</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Джандаулетова Н</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Новостройка Сад(AZ)</v>
+      </c>
+      <c r="E75" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F75" t="str">
+        <v>43967</v>
+      </c>
+      <c r="G75" t="str">
+        <v>110</v>
+      </c>
+      <c r="H75" t="str">
+        <v>130</v>
+      </c>
+      <c r="I75" t="str">
+        <v>20</v>
+      </c>
+      <c r="J75" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K75" t="str">
+        <v>8</v>
+      </c>
+      <c r="L75" t="str">
+        <v>19</v>
+      </c>
+      <c r="M75" t="str">
+        <v>15</v>
+      </c>
+      <c r="N75" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B76" t="str">
+        <v>41364</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Бурханова Аксулу</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E76" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F76" t="str">
+        <v>79209</v>
+      </c>
+      <c r="G76" t="str">
+        <v>35</v>
+      </c>
+      <c r="H76" t="str">
+        <v>62</v>
+      </c>
+      <c r="I76" t="str">
+        <v>27</v>
+      </c>
+      <c r="J76" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K76" t="str">
+        <v>8</v>
+      </c>
+      <c r="L76" t="str">
+        <v>28</v>
+      </c>
+      <c r="M76" t="str">
+        <v>13</v>
+      </c>
+      <c r="N76" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B77" t="str">
+        <v>40821</v>
+      </c>
+      <c r="C77" t="str">
+        <v>К/Х "Усманов М,"</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Хусанова (Карасу)(AZ)</v>
+      </c>
+      <c r="E77" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F77" t="str">
+        <v>75517</v>
+      </c>
+      <c r="G77" t="str">
+        <v>98</v>
+      </c>
+      <c r="H77" t="str">
+        <v>120</v>
+      </c>
+      <c r="I77" t="str">
+        <v>22</v>
+      </c>
+      <c r="J77" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K77" t="str">
+        <v>8</v>
+      </c>
+      <c r="L77" t="str">
+        <v>29</v>
+      </c>
+      <c r="M77" t="str">
+        <v>11</v>
+      </c>
+      <c r="N77" t="str">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B78" t="str">
+        <v>38269</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Ажикабылова Жансая</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>519</v>
+      </c>
+      <c r="F78" t="str">
+        <v>61898</v>
+      </c>
+      <c r="G78" t="str">
+        <v>1</v>
+      </c>
+      <c r="H78" t="str">
+        <v>55</v>
+      </c>
+      <c r="I78" t="str">
+        <v>54</v>
+      </c>
+      <c r="J78" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K78" t="str">
+        <v>9</v>
+      </c>
+      <c r="L78" t="str">
+        <v>10</v>
+      </c>
+      <c r="M78" t="str">
+        <v>14</v>
+      </c>
+      <c r="N78" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B79" t="str">
+        <v>40236</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Кемельбеков Берикжан</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E79" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F79" t="str">
+        <v>82138</v>
+      </c>
+      <c r="G79" t="str">
+        <v>50</v>
+      </c>
+      <c r="H79" t="str">
+        <v>172</v>
+      </c>
+      <c r="I79" t="str">
+        <v>122</v>
+      </c>
+      <c r="J79" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K79" t="str">
+        <v>9</v>
+      </c>
+      <c r="L79" t="str">
+        <v>10</v>
+      </c>
+      <c r="M79" t="str">
+        <v>20</v>
+      </c>
+      <c r="N79" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B80" t="str">
+        <v>42510</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Абенова С</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E80" t="str">
+        <v>626</v>
+      </c>
+      <c r="F80" t="str">
+        <v>83804</v>
+      </c>
+      <c r="G80" t="str">
+        <v>1</v>
+      </c>
+      <c r="H80" t="str">
+        <v>13</v>
+      </c>
+      <c r="I80" t="str">
+        <v>12</v>
+      </c>
+      <c r="J80" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K80" t="str">
+        <v>9</v>
+      </c>
+      <c r="L80" t="str">
+        <v>25</v>
+      </c>
+      <c r="M80" t="str">
+        <v>11</v>
+      </c>
+      <c r="N80" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B81" t="str">
+        <v>39191</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Кулмаев Батырхан</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E81" t="str">
+        <v>374</v>
+      </c>
+      <c r="F81" t="str">
+        <v>66185</v>
+      </c>
+      <c r="G81" t="str">
+        <v>21</v>
+      </c>
+      <c r="H81" t="str">
+        <v>29</v>
+      </c>
+      <c r="I81" t="str">
+        <v>8</v>
+      </c>
+      <c r="J81" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K81" t="str">
+        <v>9</v>
+      </c>
+      <c r="L81" t="str">
+        <v>29</v>
+      </c>
+      <c r="M81" t="str">
+        <v>15</v>
+      </c>
+      <c r="N81" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B82" t="str">
+        <v>41321</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Абдукаримова Садокат</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E82" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F82" t="str">
+        <v>82231</v>
+      </c>
+      <c r="G82" t="str">
+        <v>45</v>
+      </c>
+      <c r="H82" t="str">
+        <v>81</v>
+      </c>
+      <c r="I82" t="str">
+        <v>36</v>
+      </c>
+      <c r="J82" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K82" t="str">
+        <v>9</v>
+      </c>
+      <c r="L82" t="str">
+        <v>29</v>
+      </c>
+      <c r="M82" t="str">
+        <v>15</v>
+      </c>
+      <c r="N82" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B83" t="str">
+        <v>41937</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Iman Altyn Khazina</v>
+      </c>
+      <c r="D83" t="str">
+        <v>14 га  (Айтеке би)</v>
+      </c>
+      <c r="E83" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F83" t="str">
+        <v>81937</v>
+      </c>
+      <c r="G83" t="str">
+        <v>1</v>
+      </c>
+      <c r="H83" t="str">
+        <v>39</v>
+      </c>
+      <c r="I83" t="str">
+        <v>38</v>
+      </c>
+      <c r="J83" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K83" t="str">
+        <v>10</v>
+      </c>
+      <c r="L83" t="str">
+        <v>4</v>
+      </c>
+      <c r="M83" t="str">
+        <v>15</v>
+      </c>
+      <c r="N83" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B84" t="str">
+        <v>37904</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Байсеитова Венера</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E84" t="str">
+        <v>1143</v>
+      </c>
+      <c r="F84" t="str">
+        <v>60935</v>
+      </c>
+      <c r="G84" t="str">
+        <v>1</v>
+      </c>
+      <c r="H84" t="str">
+        <v>18</v>
+      </c>
+      <c r="I84" t="str">
+        <v>17</v>
+      </c>
+      <c r="J84" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K84" t="str">
+        <v>10</v>
+      </c>
+      <c r="L84" t="str">
+        <v>7</v>
+      </c>
+      <c r="M84" t="str">
+        <v>22</v>
+      </c>
+      <c r="N84" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B85" t="str">
+        <v>42112</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Джумалиева Мери</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E85" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F85" t="str">
+        <v>82768</v>
+      </c>
+      <c r="G85" t="str">
+        <v>55</v>
+      </c>
+      <c r="H85" t="str">
+        <v>57</v>
+      </c>
+      <c r="I85" t="str">
+        <v>2</v>
+      </c>
+      <c r="J85" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K85" t="str">
+        <v>10</v>
+      </c>
+      <c r="L85" t="str">
+        <v>7</v>
+      </c>
+      <c r="M85" t="str">
+        <v>22</v>
+      </c>
+      <c r="N85" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B86" t="str">
+        <v>36261</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Бекбердиева Гульзира</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Амангельды (Карасу)(AZ)</v>
+      </c>
+      <c r="E86" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F86" t="str">
+        <v>58585</v>
+      </c>
+      <c r="G86" t="str">
+        <v>18</v>
+      </c>
+      <c r="H86" t="str">
+        <v>80</v>
+      </c>
+      <c r="I86" t="str">
+        <v>62</v>
+      </c>
+      <c r="J86" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K86" t="str">
+        <v>10</v>
+      </c>
+      <c r="L86" t="str">
+        <v>10</v>
+      </c>
+      <c r="M86" t="str">
+        <v>18</v>
+      </c>
+      <c r="N86" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B87" t="str">
+        <v>40796</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Агабекова Майра</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Темир казык (Карасу)</v>
+      </c>
+      <c r="E87" t="str">
+        <v>236</v>
+      </c>
+      <c r="F87" t="str">
+        <v>83882</v>
+      </c>
+      <c r="G87" t="str">
+        <v>1</v>
+      </c>
+      <c r="H87" t="str">
+        <v>45</v>
+      </c>
+      <c r="I87" t="str">
+        <v>44</v>
+      </c>
+      <c r="J87" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K87" t="str">
+        <v>10</v>
+      </c>
+      <c r="L87" t="str">
+        <v>14</v>
+      </c>
+      <c r="M87" t="str">
+        <v>12</v>
+      </c>
+      <c r="N87" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B88" t="str">
+        <v>40041</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Тажиев Меирхан</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Темир казык (Карасу)</v>
+      </c>
+      <c r="E88" t="str">
+        <v>246</v>
+      </c>
+      <c r="F88" t="str">
+        <v>71262</v>
+      </c>
+      <c r="G88" t="str">
+        <v>36</v>
+      </c>
+      <c r="H88" t="str">
+        <v>39</v>
+      </c>
+      <c r="I88" t="str">
+        <v>3</v>
+      </c>
+      <c r="J88" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K88" t="str">
+        <v>10</v>
+      </c>
+      <c r="L88" t="str">
+        <v>14</v>
+      </c>
+      <c r="M88" t="str">
+        <v>12</v>
+      </c>
+      <c r="N88" t="str">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B89" t="str">
+        <v>41326</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Акрамова Рахима</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E89" t="str">
+        <v>771</v>
+      </c>
+      <c r="F89" t="str">
+        <v>82652</v>
+      </c>
+      <c r="G89" t="str">
+        <v>29</v>
+      </c>
+      <c r="H89" t="str">
+        <v>34</v>
+      </c>
+      <c r="I89" t="str">
+        <v>5</v>
+      </c>
+      <c r="J89" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K89" t="str">
+        <v>10</v>
+      </c>
+      <c r="L89" t="str">
+        <v>14</v>
+      </c>
+      <c r="M89" t="str">
+        <v>12</v>
+      </c>
+      <c r="N89" t="str">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B90" t="str">
+        <v>23118</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Абсадикова  Шахизада</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Уалиханов(Айтеке би)</v>
+      </c>
+      <c r="E90" t="str">
+        <v>8</v>
+      </c>
+      <c r="F90" t="str">
+        <v>48499</v>
+      </c>
+      <c r="G90" t="str">
+        <v>1412</v>
+      </c>
+      <c r="H90" t="str">
+        <v>1423</v>
+      </c>
+      <c r="I90" t="str">
+        <v>11</v>
+      </c>
+      <c r="J90" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K90" t="str">
+        <v>10</v>
+      </c>
+      <c r="L90" t="str">
+        <v>23</v>
+      </c>
+      <c r="M90" t="str">
+        <v>11</v>
+      </c>
+      <c r="N90" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B91" t="str">
+        <v>29442</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Чугунов М</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Жибек-Жолы(AZ)</v>
+      </c>
+      <c r="E91" t="str">
+        <v>167</v>
+      </c>
+      <c r="F91" t="str">
+        <v>50968</v>
+      </c>
+      <c r="G91" t="str">
+        <v>642</v>
+      </c>
+      <c r="H91" t="str">
+        <v>646</v>
+      </c>
+      <c r="I91" t="str">
+        <v>4</v>
+      </c>
+      <c r="J91" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K91" t="str">
+        <v>10</v>
+      </c>
+      <c r="L91" t="str">
+        <v>28</v>
+      </c>
+      <c r="M91" t="str">
+        <v>14</v>
+      </c>
+      <c r="N91" t="str">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B92" t="str">
+        <v>30788</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Мирзаев Х</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Навои (Карасу)(AZ)</v>
+      </c>
+      <c r="E92" t="str">
+        <v>54</v>
+      </c>
+      <c r="F92" t="str">
+        <v>40830</v>
+      </c>
+      <c r="G92" t="str">
+        <v>2360</v>
+      </c>
+      <c r="H92" t="str">
+        <v>2373</v>
+      </c>
+      <c r="I92" t="str">
+        <v>13</v>
+      </c>
+      <c r="J92" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K92" t="str">
+        <v>10</v>
+      </c>
+      <c r="L92" t="str">
+        <v>29</v>
+      </c>
+      <c r="M92" t="str">
+        <v>13</v>
+      </c>
+      <c r="N92" t="str">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B93" t="str">
+        <v>31757</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Алиев Махамбет</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Молшылык (Карасу)</v>
+      </c>
+      <c r="E93" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F93" t="str">
+        <v>53158</v>
+      </c>
+      <c r="G93" t="str">
+        <v>247</v>
+      </c>
+      <c r="H93" t="str">
+        <v>253</v>
+      </c>
+      <c r="I93" t="str">
+        <v>6</v>
+      </c>
+      <c r="J93" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K93" t="str">
+        <v>11</v>
+      </c>
+      <c r="L93" t="str">
+        <v>7</v>
+      </c>
+      <c r="M93" t="str">
+        <v>22</v>
+      </c>
+      <c r="N93" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B94" t="str">
+        <v>35123</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Абдукадырова Дильфуз</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Новостройка (Акбай)</v>
+      </c>
+      <c r="E94" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F94" t="str">
+        <v>84618</v>
+      </c>
+      <c r="G94" t="str">
+        <v>1</v>
+      </c>
+      <c r="H94" t="str">
+        <v>91</v>
+      </c>
+      <c r="I94" t="str">
+        <v>90</v>
+      </c>
+      <c r="J94" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K94" t="str">
+        <v>12</v>
+      </c>
+      <c r="L94" t="str">
+        <v>8</v>
+      </c>
+      <c r="M94" t="str">
+        <v>18</v>
+      </c>
+      <c r="N94" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B95" t="str">
+        <v>40399</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Алтынбек Айнур</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E95" t="str">
+        <v>б\н</v>
+      </c>
+      <c r="F95" t="str">
+        <v>73254</v>
+      </c>
+      <c r="G95" t="str">
+        <v>41</v>
+      </c>
+      <c r="H95" t="str">
+        <v>66</v>
+      </c>
+      <c r="I95" t="str">
+        <v>25</v>
+      </c>
+      <c r="J95" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K95" t="str">
+        <v>12</v>
+      </c>
+      <c r="L95" t="str">
+        <v>9</v>
+      </c>
+      <c r="M95" t="str">
+        <v>16</v>
+      </c>
+      <c r="N95" t="str">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B96" t="str">
+        <v>37213</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Бабешко Виктория</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Жанакурылыс (Инфра Карасу)</v>
+      </c>
+      <c r="E96" t="str">
+        <v>б/н</v>
+      </c>
+      <c r="F96" t="str">
+        <v>59769</v>
+      </c>
+      <c r="G96" t="str">
+        <v>60</v>
+      </c>
+      <c r="H96" t="str">
+        <v>68</v>
+      </c>
+      <c r="I96" t="str">
+        <v>8</v>
+      </c>
+      <c r="J96" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K96" t="str">
+        <v>12</v>
+      </c>
+      <c r="L96" t="str">
+        <v>9</v>
+      </c>
+      <c r="M96" t="str">
+        <v>16</v>
+      </c>
+      <c r="N96" t="str">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Abylai</v>
+      </c>
+      <c r="B97" t="str">
+        <v>39972</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Дакенова Насиба</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Жузимдик (Карасу)</v>
+      </c>
+      <c r="E97" t="str">
+        <v>9</v>
+      </c>
+      <c r="F97" t="str">
+        <v>82983</v>
+      </c>
+      <c r="G97" t="str">
+        <v>50</v>
+      </c>
+      <c r="H97" t="str">
+        <v>111</v>
+      </c>
+      <c r="I97" t="str">
+        <v>61</v>
+      </c>
+      <c r="J97" t="str">
+        <v>2025</v>
+      </c>
+      <c r="K97" t="str">
+        <v>12</v>
+      </c>
+      <c r="L97" t="str">
+        <v>16</v>
+      </c>
+      <c r="M97" t="str">
+        <v>15</v>
+      </c>
+      <c r="N97" t="str">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N97"/>
   </ignoredErrors>
 </worksheet>
 </file>